--- a/client/src/assets/customer-template.xlsx
+++ b/client/src/assets/customer-template.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G5"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -418,7 +418,6 @@
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,9 +442,6 @@
       <c r="G1" s="2" t="str">
         <v>合作状态</v>
       </c>
-      <c r="H1" s="2" t="str">
-        <v>付费金额</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -469,9 +465,6 @@
       <c r="G2" s="2" t="str">
         <v>合作中</v>
       </c>
-      <c r="H2" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="str">
@@ -495,9 +488,6 @@
       <c r="G3" s="2" t="str">
         <v>合作中</v>
       </c>
-      <c r="H3" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="str">
@@ -521,9 +511,6 @@
       <c r="G4" s="2" t="str">
         <v>合作中</v>
       </c>
-      <c r="H4" s="2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="str">
@@ -547,13 +534,10 @@
       <c r="G5" s="2" t="str">
         <v>合作中</v>
       </c>
-      <c r="H5" s="2" t="str">
-        <v>400</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>